--- a/Main/Tasks/Task3/JetstarFC3.xlsx
+++ b/Main/Tasks/Task3/JetstarFC3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AE\4th Year\Second Term\Design of control systems for Aeronautical and Space vehicles_AER4420\Autopilot_Team3\Autopilot_Team3\Main\Tasks\Task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64392F4-02B2-4DEA-9D59-27C3E9313B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C55D864-958F-49A1-86EA-FC9E642C066F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2255,7 +2255,7 @@
         <v>123</v>
       </c>
       <c r="B61" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C61" s="23" t="s">
         <v>132</v>
